--- a/05-comparable-company-analysis/Trading_Comps.xlsx
+++ b/05-comparable-company-analysis/Trading_Comps.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Cover!$A$1:$F$7</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Trading Comps'!$A$1:$U$33</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Trading Comps'!$A$1:$U$41</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Valuation Range'!$A$1:$T$29</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,10 +26,68 @@
 </workbook>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Valeur reprise de l'onglet DCF du modèle Danone (scénario central).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Multiple médian VE/EBITDA des comparables boursiers (cf. onglet Trading Comps), à titre indicatif.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Comparable le moins cher du groupe : General Mills.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Multiple médian des comparables boursiers, à titre indicatif ; exclu du calcul des bornes haute/basse.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
-  <si>
-    <t xml:space="preserve">Trading Comps - consolidation des comparables boursiers utilisés dans le portfolio</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="70">
+  <si>
+    <t xml:space="preserve">Trading Comps - comparables boursiers du portfolio</t>
   </si>
   <si>
     <t xml:space="preserve">Exercice personnel - Yvann Ahoure</t>
@@ -86,6 +144,9 @@
     <t xml:space="preserve">Calculé : VE DCF / EBITDA</t>
   </si>
   <si>
+    <t xml:space="preserve">Médiane pairs cotés (hors Danone)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nestlé</t>
   </si>
   <si>
@@ -164,6 +225,9 @@
     <t xml:space="preserve">Note méthodologique : les multiples calculés ci-dessus (lignes 'implicite marché' / 'implicite DCF') sont saisis en dur, recalculés manuellement à chaque mise à jour des 3 modèles DCF sources, plutôt que liés par formule inter-classeurs. Ce choix évite la fragilité des liens externes Excel (chemins relatifs rompus en cas de déplacement/zip du portfolio, valeurs en cache perdues lors d'un recalcul hors Excel) ; la cellule Source de chaque ligne indique le fichier et le calcul d'origine pour permettre une vérification manuelle rapide.</t>
   </si>
   <si>
+    <t xml:space="preserve">Lecture complémentaire (bonnes pratiques de valorisation par multiples) : la médiane est ajoutée à côté de la moyenne du groupe agroalimentaire (colonne I), car une moyenne peut être tirée par une valeur isolée alors que la médiane limite cet effet (BIWS Valuation Guide, p. 13 et p. 25 ; Vernimmen, chapitre 32, section 3.7). Un multiple ne se lit jamais dans l'absolu : il devrait en principe être mis en regard de la croissance attendue et de la marge de chaque comparable (BIWS, p. 18-19 ; Vernimmen, section 32.3.7 sur les régressions multiple/croissance). Ces données de croissance et de marge par comparable ne sont pas disponibles dans les sources utilisées ici (voir sources.md) : la dispersion des multiples du groupe (9,25x à 14,1x) est donc signalée sans être expliquée chiffre par chiffre. Enfin, ces multiples sont des multiples de marché (participations minoritaires) et non des multiples de transactions : ils n'intègrent pas de prime de contrôle, laquelle s'observe en moyenne autour de 25% du cours avant annonce dans les acquisitions de sociétés cotées (Vernimmen, chapitre 32, section 3.6).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fourchette de valorisation - Danone (comparables vs DCF)</t>
   </si>
   <si>
@@ -203,7 +267,7 @@
     <t xml:space="preserve">Multiple General Mills (EV/EBITDA FY2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">DCF (scénario central, onglet DCF du modèle Danone)</t>
+    <t xml:space="preserve">DCF (scénario central, cf. modèle Danone)</t>
   </si>
   <si>
     <t xml:space="preserve">n/a (DCF)</t>
@@ -212,10 +276,13 @@
     <t xml:space="preserve">Cours de marché actuel (12/10/2026)</t>
   </si>
   <si>
+    <t xml:space="preserve">Multiple médian pairs cotés (indicatif)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Synthèse de la fourchette</t>
   </si>
   <si>
-    <t xml:space="preserve">Borne basse (comparable le moins cher, General Mills)</t>
+    <t xml:space="preserve">Borne basse (comparable le moins cher)</t>
   </si>
   <si>
     <t xml:space="preserve">Borne haute (DCF, scénario central)</t>
@@ -224,7 +291,10 @@
     <t xml:space="preserve">Cours de marché actuel, pour mémoire</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture : le cours de marché actuel (59,5 €) se situe dans le bas de la fourchette formée par les comparables boursiers (45,8 € à 76,3 €) et nettement sous le DCF (84,1 €). Les trois méthodes convergent vers une lecture favorable à Danone sans pour autant constituer une recommandation d'investissement - voir l'avertissement du modèle DCF.</t>
+    <t xml:space="preserve">Multiple médian pairs cotés (hors bornes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecture : le cours de marché actuel (59,5 €) se situe dans le bas de la fourchette formée par les comparables boursiers (45,8 € à 76,3 €) et nettement sous le DCF (84,1 €). Les trois méthodes convergent vers une lecture favorable à Danone sans pour autant constituer une recommandation d'investissement ; voir l'avertissement du modèle DCF. Le multiple médian des trois comparables (12,7x, soit la valeur d'Unilever) situe un point de référence à 67,5 € par action, au centre de la fourchette formée par les comparables boursiers.</t>
   </si>
 </sst>
 </file>
@@ -239,7 +309,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="169" formatCode="#,##0.0&quot; €&quot;"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,6 +412,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -397,7 +479,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -470,6 +552,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -483,6 +569,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -697,11 +787,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="81574732"/>
-        <c:axId val="40365501"/>
+        <c:axId val="62881147"/>
+        <c:axId val="61331221"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81574732"/>
+        <c:axId val="62881147"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -732,7 +822,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40365501"/>
+        <c:crossAx val="61331221"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -740,7 +830,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40365501"/>
+        <c:axId val="61331221"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -815,7 +905,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81574732"/>
+        <c:crossAx val="62881147"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -934,9 +1024,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Valuation Range'!$B$10:$B$14</c:f>
+              <c:f>'Valuation Range'!$B$10:$B$15</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>Multiple Nestlé (EV/EBITDA FY2025)</c:v>
                 </c:pt>
@@ -947,20 +1037,23 @@
                   <c:v>Multiple General Mills (EV/EBITDA FY2026)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>DCF (scénario central, onglet DCF du modèle Danone)</c:v>
+                  <c:v>DCF (scénario central, cf. modèle Danone)</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Cours de marché actuel (12/10/2026)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Multiple médian pairs cotés (indicatif)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Valuation Range'!$F$10:$F$14</c:f>
+              <c:f>'Valuation Range'!$F$10:$F$15</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.0" €"</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>76.2863289138643</c:v>
                 </c:pt>
@@ -976,17 +1069,20 @@
                 <c:pt idx="4">
                   <c:v>59.5</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>67.4869025668042</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74561300"/>
-        <c:axId val="90181474"/>
+        <c:axId val="13521047"/>
+        <c:axId val="64488189"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74561300"/>
+        <c:axId val="13521047"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1017,7 +1113,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90181474"/>
+        <c:crossAx val="64488189"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1025,7 +1121,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90181474"/>
+        <c:axId val="64488189"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1100,7 +1196,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74561300"/>
+        <c:crossAx val="13521047"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1139,9 +1235,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>470160</xdr:colOff>
+      <xdr:colOff>465840</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>133560</xdr:rowOff>
+      <xdr:rowOff>129240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1149,8 +1245,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="11232000" y="800280"/>
-        <a:ext cx="7196760" cy="2876760"/>
+        <a:off x="13016880" y="800280"/>
+        <a:ext cx="7192440" cy="2872440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1174,9 +1270,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>470160</xdr:colOff>
+      <xdr:colOff>465840</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>167760</xdr:rowOff>
+      <xdr:rowOff>163440</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1185,7 +1281,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8694360" y="1562040"/>
-        <a:ext cx="7196760" cy="3596760"/>
+        <a:ext cx="7192440" cy="3754440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1437,7 +1533,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:I33"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -1446,6 +1542,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="34"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1530,13 +1627,20 @@
       <c r="G8" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="H8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <f aca="false">MEDIAN(D9:D11)</f>
+        <v>12.7</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>14.1</v>
@@ -1548,15 +1652,15 @@
         <v>14</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="13" t="n">
         <v>12.7</v>
@@ -1568,30 +1672,30 @@
         <v>14</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>9.25</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1621,10 +1725,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>4.88</v>
@@ -1634,15 +1738,15 @@
         <v>14</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>6.52</v>
@@ -1652,30 +1756,30 @@
         <v>14</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>4.9</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -1705,10 +1809,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D23" s="10" t="n">
         <v>100.32</v>
@@ -1718,15 +1822,15 @@
         <v>14</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>8.63</v>
@@ -1736,12 +1840,12 @@
         <v>14</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -1783,7 +1887,7 @@
     </row>
     <row r="33" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
@@ -1791,10 +1895,61 @@
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
     </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B27:G31"/>
     <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B35:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1821,17 +1976,17 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>4295</v>
@@ -1839,7 +1994,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>8430</v>
@@ -1847,151 +2002,181 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" s="17" t="n">
         <v>683.34</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="D9" s="18" t="s">
         <v>54</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="18" t="n">
+        <v>57</v>
+      </c>
+      <c r="C10" s="19" t="n">
         <v>14.1</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="20" t="n">
         <f aca="false">$C$5*C10</f>
         <v>60559.5</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">D10-$C$6</f>
         <v>52129.5</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="21" t="n">
         <f aca="false">E10/$C$7</f>
         <v>76.2863289138643</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="18" t="n">
+        <v>58</v>
+      </c>
+      <c r="C11" s="19" t="n">
         <v>12.7</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="20" t="n">
         <f aca="false">$C$5*C11</f>
         <v>54546.5</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="20" t="n">
         <f aca="false">D11-$C$6</f>
         <v>46116.5</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="21" t="n">
         <f aca="false">E11/$C$7</f>
         <v>67.4869025668042</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="18" t="n">
+        <v>59</v>
+      </c>
+      <c r="C12" s="19" t="n">
         <v>9.25</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="20" t="n">
         <f aca="false">$C$5*C12</f>
         <v>39728.75</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="20" t="n">
         <f aca="false">D12-$C$6</f>
         <v>31298.75</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="21" t="n">
         <f aca="false">E12/$C$7</f>
         <v>45.8026019258349</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>65913.77</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="20" t="n">
         <f aca="false">D13-$C$6</f>
         <v>57483.77</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="21" t="n">
         <f aca="false">E13/$C$7</f>
         <v>84.1217695437118</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="F14" s="22" t="n">
         <v>59.5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <f aca="false">'Trading Comps'!I8</f>
+        <v>12.7</v>
+      </c>
+      <c r="D15" s="20" t="n">
+        <f aca="false">$C$5*C15</f>
+        <v>54546.5</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <f aca="false">D15-$C$6</f>
+        <v>46116.5</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <f aca="false">E15/$C$7</f>
+        <v>67.4869025668042</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="C18" s="21" t="n">
         <f aca="false">F12</f>
         <v>45.8026019258349</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="C19" s="21" t="n">
         <f aca="false">F13</f>
         <v>84.1217695437118</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="C20" s="21" t="n">
         <f aca="false">F14</f>
         <v>59.5</v>
       </c>
     </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <f aca="false">F15</f>
+        <v>67.4869025668042</v>
+      </c>
+    </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -2030,6 +2215,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>